--- a/artfynd/A 9032-2025 artfynd.xlsx
+++ b/artfynd/A 9032-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122768780</v>
+        <v>122774977</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357471</v>
+        <v>357463</v>
       </c>
       <c r="R2" t="n">
-        <v>6630943</v>
+        <v>6631003</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122774977</v>
+        <v>122768780</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357463</v>
+        <v>357471</v>
       </c>
       <c r="R3" t="n">
-        <v>6631003</v>
+        <v>6630943</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +850,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 9032-2025 artfynd.xlsx
+++ b/artfynd/A 9032-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122774977</v>
+        <v>122768780</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357463</v>
+        <v>357471</v>
       </c>
       <c r="R2" t="n">
-        <v>6631003</v>
+        <v>6630943</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122768780</v>
+        <v>122774977</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357471</v>
+        <v>357463</v>
       </c>
       <c r="R3" t="n">
-        <v>6630943</v>
+        <v>6631003</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +860,9 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 9032-2025 artfynd.xlsx
+++ b/artfynd/A 9032-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122774977</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122768780</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
